--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487805_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487805_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6478</v>
+        <v>2.051</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1829</v>
+        <v>2.498</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5351</v>
+        <v>-0.447</v>
       </c>
       <c r="G2" t="n">
         <v>0.5678</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1246</v>
+        <v>-0.7214</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7235</v>
+        <v>0.0386</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8481</v>
+        <v>-0.76</v>
       </c>
       <c r="V2" t="n">
         <v>1.164</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5272</v>
+        <v>1.1385</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1372</v>
+        <v>2.631</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.61</v>
+        <v>-1.4926</v>
       </c>
       <c r="G3" t="n">
         <v>2.1763</v>
@@ -688,13 +688,13 @@
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6643</v>
+        <v>-1.053</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7581</v>
+        <v>-0.2643</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9061</v>
+        <v>-0.7887</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8173</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1646</v>
+        <v>0.0721</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1314</v>
+        <v>0.891</v>
       </c>
       <c r="F4" t="n">
-        <v>0.296</v>
+        <v>-0.819</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.1487</v>
+        <v>-1.7922</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.676</v>
+        <v>-0.6672</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4727</v>
+        <v>-1.125</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4791</v>
+        <v>0.7715</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.431</v>
+        <v>0.1535</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0482</v>
+        <v>0.618</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6696</v>
+        <v>-2.5637</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.245</v>
+        <v>-0.8207</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4245</v>
+        <v>-1.7431</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4808</v>
+        <v>-0.5926</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3477</v>
+        <v>-0.1105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1331</v>
+        <v>-0.4821</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3962</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5696</v>
+        <v>1.4283</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9658</v>
+        <v>-1.5017</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7922</v>
+        <v>0.1869</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6672</v>
+        <v>0.9405</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.125</v>
+        <v>-0.7536</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7715</v>
+        <v>1.6199</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1535</v>
+        <v>0.6672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.618</v>
+        <v>0.9527</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5637</v>
+        <v>-1.433</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8207</v>
+        <v>0.2733</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7431</v>
+        <v>-1.7063</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0608</v>
+        <v>-1.3806</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4319</v>
+        <v>-0.3186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6289</v>
+        <v>-1.0621</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5838</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3538</v>
+        <v>-0.4635</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4828</v>
+        <v>-0.2936</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9752</v>
+        <v>4.1057</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.458</v>
+        <v>-4.3993</v>
       </c>
       <c r="G6" t="n">
         <v>-1.401</v>
@@ -922,13 +922,13 @@
         <v>2.0812</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3523</v>
+        <v>-0.1631</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0743</v>
+        <v>0.2048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4266</v>
+        <v>-0.3679</v>
       </c>
       <c r="V6" t="n">
         <v>0.23</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7603</v>
+        <v>-0.3815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.5601</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7366</v>
+        <v>0.1786</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1869</v>
+        <v>-1.1487</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9405</v>
+        <v>-0.676</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7536</v>
+        <v>-0.4727</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6199</v>
+        <v>-0.4791</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6672</v>
+        <v>-0.431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9527</v>
+        <v>-0.0482</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.433</v>
+        <v>-0.6696</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2733</v>
+        <v>-0.245</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7063</v>
+        <v>-0.4245</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0675</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7705</v>
+        <v>-0.0809</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2969</v>
+        <v>0.0157</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7040999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4635</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8056</v>
+        <v>-0.6397</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1464</v>
+        <v>-0.0393</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6592</v>
+        <v>-0.6004</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7919</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6381</v>
+        <v>-0.4722</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9457</v>
+        <v>-0.6764</v>
       </c>
       <c r="E9" t="n">
-        <v>1.42</v>
+        <v>1.8067</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3657</v>
+        <v>-2.4831</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6962</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7927</v>
+        <v>-0.5234</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.64</v>
+        <v>-0.2533</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1526</v>
+        <v>-0.2701</v>
       </c>
       <c r="V9" t="n">
         <v>2.3351</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9355</v>
+        <v>-3.3044</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7366</v>
+        <v>-1.6358</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1989</v>
+        <v>-1.6686</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5358</v>
@@ -1234,13 +1234,13 @@
         <v>2.4974</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3146</v>
+        <v>-0.0543</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4502</v>
+        <v>0.5511</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1356</v>
+        <v>-0.6054</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1711</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7451</v>
+        <v>-3.9716</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5421</v>
+        <v>-1.7687</v>
       </c>
       <c r="F11" t="n">
         <v>-2.203</v>
@@ -1312,10 +1312,10 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3387</v>
+        <v>-0.5653</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6153</v>
+        <v>0.1582</v>
       </c>
       <c r="U11" t="n">
         <v>-0.7235</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.731599999999999</v>
+        <v>-6.079</v>
       </c>
       <c r="E12" t="n">
-        <v>8.704700000000001</v>
+        <v>9.3568</v>
       </c>
       <c r="F12" t="n">
-        <v>-15.4363</v>
+        <v>-15.4361</v>
       </c>
       <c r="G12" t="n">
         <v>-11.8376</v>
       </c>
       <c r="H12" t="n">
-        <v>2.408700000000001</v>
+        <v>2.4087</v>
       </c>
       <c r="I12" t="n">
         <v>-14.2466</v>
@@ -1369,7 +1369,7 @@
         <v>5.615000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>3.000299999999999</v>
+        <v>3.0003</v>
       </c>
       <c r="M12" t="n">
         <v>-20.4529</v>
@@ -1390,13 +1390,13 @@
         <v>15.609</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.2436</v>
+        <v>-5.5911</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0116</v>
+        <v>-0.3592</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.2318</v>
+        <v>-5.232000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.0251</v>
@@ -1405,7 +1405,7 @@
         <v>8.385100000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.359999999999999</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.827500000000001</v>
+        <v>9.340299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0651</v>
+        <v>10.4937</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2375</v>
+        <v>-1.1534</v>
       </c>
       <c r="G13" t="n">
         <v>9.307700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>1.0406</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7685</v>
+        <v>1.2813</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3725</v>
+        <v>0.8011</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3961</v>
+        <v>0.4802</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8518</v>
+        <v>4.8955</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4455</v>
+        <v>3.767</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4063</v>
+        <v>1.1285</v>
       </c>
       <c r="G14" t="n">
         <v>7.8837</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0776</v>
+        <v>0.9661</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2296</v>
+        <v>0.5511</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3072</v>
+        <v>0.415</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1696</v>
+        <v>1.5371</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1377</v>
+        <v>2.2448</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9681</v>
+        <v>-0.7078</v>
       </c>
       <c r="G15" t="n">
         <v>0.2748</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3517</v>
+        <v>0.7191</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3477</v>
+        <v>0.4548</v>
       </c>
       <c r="U15" t="n">
-        <v>0.004</v>
+        <v>0.2643</v>
       </c>
       <c r="V15" t="n">
         <v>1.1675</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.7592</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3037</v>
+        <v>-0.0727</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6071</v>
+        <v>0.8319</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4086</v>
+        <v>0.2738</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5458</v>
+        <v>0.433</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9544</v>
+        <v>-0.1592</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5183</v>
+        <v>0.2535</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0849</v>
+        <v>0.0576</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5666</v>
+        <v>0.1959</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9268999999999999</v>
+        <v>0.0203</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5391</v>
+        <v>0.3755</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3878</v>
+        <v>-0.3551</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7981</v>
+        <v>0.0692</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8011</v>
+        <v>-0.3262</v>
       </c>
       <c r="U16" t="n">
-        <v>0.997</v>
+        <v>0.3954</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2737</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4774</v>
+        <v>0.7063</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0727</v>
+        <v>0.5181</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5501</v>
+        <v>0.1882</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2738</v>
+        <v>-0.4086</v>
       </c>
       <c r="H17" t="n">
-        <v>0.433</v>
+        <v>0.5458</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1592</v>
+        <v>-0.9544</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2535</v>
+        <v>0.5183</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0576</v>
+        <v>1.0849</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1959</v>
+        <v>-0.5666</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0203</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3755</v>
+        <v>-0.5391</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3551</v>
+        <v>-0.3878</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2127</v>
+        <v>1.5935</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3262</v>
+        <v>1.0154</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1136</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2737</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.9199000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1594</v>
+        <v>-0.315</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8186</v>
+        <v>1.6043</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.978</v>
+        <v>-1.9193</v>
       </c>
       <c r="G18" t="n">
         <v>1.1523</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8964</v>
+        <v>0.7408</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4596</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2225</v>
+        <v>0.2812</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2676</v>
+        <v>-1.4335</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.432</v>
+        <v>-0.5391</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8356</v>
+        <v>-0.8943</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9022</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6752</v>
+        <v>0.5094</v>
       </c>
       <c r="T19" t="n">
-        <v>0.531</v>
+        <v>0.4239</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1442</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8148</v>
+        <v>-1.5382</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2806</v>
+        <v>-2.426</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0954</v>
+        <v>0.8878</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5734</v>
+        <v>-1.139</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6354</v>
+        <v>0.32</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0621</v>
+        <v>-1.4589</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3404</v>
+        <v>-1.3512</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0066</v>
+        <v>0.0384</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6662</v>
+        <v>-1.3896</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2329</v>
+        <v>0.2122</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6288</v>
+        <v>0.2816</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6041</v>
+        <v>-0.0694</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9479</v>
+        <v>0.2469</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8292</v>
+        <v>-0.0343</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1188</v>
+        <v>0.2812</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.097</v>
+        <v>-1.5902</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6404</v>
+        <v>0.3878</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5433</v>
+        <v>-1.978</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.139</v>
+        <v>-1.5734</v>
       </c>
       <c r="H21" t="n">
-        <v>0.32</v>
+        <v>-1.6354</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4589</v>
+        <v>0.0621</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3512</v>
+        <v>-0.3404</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0384</v>
+        <v>-1.0066</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3896</v>
+        <v>0.6662</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2122</v>
+        <v>-1.2329</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2816</v>
+        <v>-0.6288</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0694</v>
+        <v>-0.6041</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3118</v>
+        <v>1.1725</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2486</v>
+        <v>0.9363</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0633</v>
+        <v>0.2362</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1669</v>
+        <v>-3.4869</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5299</v>
+        <v>-0.5417</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.6968</v>
+        <v>-2.9452</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0316</v>
@@ -2170,13 +2170,13 @@
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4079</v>
+        <v>1.0879</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0217</v>
+        <v>0.9502</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6139</v>
+        <v>0.1377</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7513</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.731400000000002</v>
+        <v>8.874599999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>15.436</v>
+        <v>15.4362</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.704599999999999</v>
+        <v>-6.561599999999999</v>
       </c>
       <c r="G23" t="n">
         <v>11.8375</v>
@@ -2230,7 +2230,7 @@
         <v>17.2468</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.615399999999999</v>
+        <v>-8.615400000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-5.6153</v>
@@ -2248,19 +2248,19 @@
         <v>7.284</v>
       </c>
       <c r="S23" t="n">
-        <v>6.2436</v>
+        <v>8.386699999999999</v>
       </c>
       <c r="T23" t="n">
         <v>5.2319</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0118</v>
+        <v>3.1548</v>
       </c>
       <c r="V23" t="n">
         <v>-3.025</v>
       </c>
       <c r="W23" t="n">
-        <v>5.36</v>
+        <v>5.359999999999999</v>
       </c>
       <c r="X23" t="n">
         <v>-8.385000000000002</v>
